--- a/exports/ANGELONE_full_report.xlsx
+++ b/exports/ANGELONE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.07</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.38541666666</v>
+        <v>44585.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>139.9</v>
+        <v>134.8</v>
       </c>
       <c r="I2" t="n">
         <v>138.4886976686122</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>10.16</v>
+        <v>6.14</v>
       </c>
       <c r="L2" t="n">
         <v>2.76</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>15.23</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>134.8</v>
+        <v>141.1</v>
       </c>
       <c r="I3" t="n">
         <v>135.2457718046417</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50</v>
+        <v>50.83333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-4.67</v>
       </c>
       <c r="L3" t="n">
-        <v>6.08</v>
+        <v>7.57</v>
       </c>
       <c r="M3" t="n">
         <v>4.51</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.14</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>181.7</v>
+        <v>173.2</v>
       </c>
       <c r="I4" t="n">
         <v>175.3115649025631</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>47.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K4" t="n">
-        <v>28.77</v>
+        <v>22.75</v>
       </c>
       <c r="L4" t="n">
         <v>3.9</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.9</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>144.9</v>
+        <v>149</v>
       </c>
       <c r="I5" t="n">
         <v>148.9665779233632</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>16.34</v>
+        <v>13.97</v>
       </c>
       <c r="L5" t="n">
         <v>6.24</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>12.83</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44725.55208333334</v>
+        <v>44726.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>136.5</v>
+        <v>133.3</v>
       </c>
       <c r="I6" t="n">
         <v>135.4710201245359</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.390000000000001</v>
+        <v>-10.54</v>
       </c>
       <c r="L6" t="n">
-        <v>9.93</v>
+        <v>11.21</v>
       </c>
       <c r="M6" t="n">
         <v>4.18</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.27</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44743.55208333334</v>
+        <v>44746.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>121.6</v>
+        <v>125.8</v>
       </c>
       <c r="I7" t="n">
         <v>125.7220775803506</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>8.779999999999999</v>
+        <v>5.63</v>
       </c>
       <c r="L7" t="n">
         <v>2.93</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.57</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44768.55208333334</v>
+        <v>44769.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>134.7</v>
+        <v>133.1</v>
       </c>
       <c r="I8" t="n">
         <v>133.5852527174072</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K8" t="n">
-        <v>7.07</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
         <v>3.42</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.68</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44809.55208333334</v>
+        <v>44810.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>133.9</v>
+        <v>139.5</v>
       </c>
       <c r="I9" t="n">
         <v>134.7608145316348</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6</v>
+        <v>-4.81</v>
       </c>
       <c r="L9" t="n">
-        <v>4.36</v>
+        <v>7.74</v>
       </c>
       <c r="M9" t="n">
         <v>1.47</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.4</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>149.2</v>
+        <v>140.4</v>
       </c>
       <c r="I10" t="n">
         <v>146.4340648372703</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>6.95</v>
+        <v>0.65</v>
       </c>
       <c r="L10" t="n">
         <v>3.37</v>
@@ -1011,7 +1130,7 @@
         <v>2.46</v>
       </c>
       <c r="N10" t="n">
-        <v>2.71</v>
+        <v>7.71</v>
       </c>
       <c r="O10" t="n">
         <v>3.81</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.76</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>137.2</v>
+        <v>146.4</v>
       </c>
       <c r="I11" t="n">
         <v>145.8570571572503</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.28</v>
+        <v>-4.27</v>
       </c>
       <c r="L11" t="n">
         <v>5.91</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.53</v>
+        <v>12.1</v>
       </c>
       <c r="O11" t="n">
         <v>-7.71</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.37</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44872.55208333334</v>
+        <v>44874.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>154.9</v>
+        <v>151.9</v>
       </c>
       <c r="I12" t="n">
         <v>154.1213585032494</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n">
-        <v>5.81</v>
+        <v>3.76</v>
       </c>
       <c r="L12" t="n">
         <v>2.25</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.32</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44879.55208333334</v>
+        <v>44880.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>151.3</v>
+        <v>153.9</v>
       </c>
       <c r="I13" t="n">
         <v>153.1343096242033</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>0.39</v>
+        <v>-1.32</v>
       </c>
       <c r="L13" t="n">
         <v>3.29</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.84</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>153.2</v>
+        <v>152.5</v>
       </c>
       <c r="I14" t="n">
         <v>152.9563037064708</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.45</v>
+        <v>-0.91</v>
       </c>
       <c r="L14" t="n">
         <v>6.95</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.15</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>105.9</v>
+        <v>113.6</v>
       </c>
       <c r="I15" t="n">
         <v>106.5768379063515</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>85</v>
       </c>
       <c r="K15" t="n">
-        <v>30.56</v>
+        <v>25.51</v>
       </c>
       <c r="L15" t="n">
         <v>1.97</v>
@@ -1296,7 +1475,7 @@
         <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>5.27</v>
+        <v>5.38</v>
       </c>
       <c r="O15" t="n">
         <v>-0.85</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>10.96</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45000.55208333334</v>
+        <v>45001.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>107.7</v>
+        <v>104.5</v>
       </c>
       <c r="I16" t="n">
         <v>105.6345721173449</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.19</v>
+        <v>-8.01</v>
       </c>
       <c r="L16" t="n">
-        <v>6.87</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>12.53</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45007.55208333334</v>
+        <v>45008.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>113.8</v>
+        <v>117.4</v>
       </c>
       <c r="I17" t="n">
         <v>115.5782410886027</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.9</v>
+        <v>-12.34</v>
       </c>
       <c r="L17" t="n">
-        <v>9.19</v>
+        <v>12.92</v>
       </c>
       <c r="M17" t="n">
         <v>1.44</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.59</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45035.55208333334</v>
+        <v>45036.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>126</v>
+        <v>123.8</v>
       </c>
       <c r="I18" t="n">
         <v>124.8198872689297</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>7.33</v>
+        <v>5.45</v>
       </c>
       <c r="L18" t="n">
         <v>5.03</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45051.55208333334</v>
+        <v>45054.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>122.3</v>
+        <v>127.3</v>
       </c>
       <c r="I19" t="n">
         <v>127.0208870552576</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>1.21</v>
+        <v>-2.83</v>
       </c>
       <c r="L19" t="n">
-        <v>3.07</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
         <v>0.57</v>
       </c>
       <c r="N19" t="n">
-        <v>0.49</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
         <v>-1.59</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.29</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45063.55208333334</v>
+        <v>45064.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>127.1</v>
+        <v>124</v>
       </c>
       <c r="I20" t="n">
         <v>125.1496116124668</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.16</v>
+        <v>-2.59</v>
       </c>
       <c r="L20" t="n">
         <v>4.16</v>
       </c>
       <c r="M20" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="N20" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
         <v>3.68</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>6.73</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45072.38541666666</v>
+        <v>45072.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>125.6</v>
+        <v>127.9</v>
       </c>
       <c r="I21" t="n">
         <v>126.805473538099</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.29</v>
+        <v>-3.15</v>
       </c>
       <c r="L21" t="n">
-        <v>2.34</v>
+        <v>3.55</v>
       </c>
       <c r="M21" t="n">
         <v>0.42</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>6.89</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45121.55208333334</v>
+        <v>45124.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>170.7</v>
+        <v>160.3</v>
       </c>
       <c r="I22" t="n">
         <v>169.7529347702014</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>49</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>33.46</v>
+        <v>25.33</v>
       </c>
       <c r="L22" t="n">
         <v>1.88</v>
       </c>
       <c r="M22" t="n">
-        <v>0.68</v>
+        <v>4.98</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>7.09</v>
       </c>
       <c r="O22" t="n">
         <v>3.56</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.21</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45145.55208333334</v>
+        <v>45146.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>151.6</v>
+        <v>159.1</v>
       </c>
       <c r="I23" t="n">
         <v>157.7112703511917</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>5.43</v>
+        <v>0.75</v>
       </c>
       <c r="L23" t="n">
         <v>3.18</v>
@@ -1752,7 +2027,7 @@
         <v>1.86</v>
       </c>
       <c r="N23" t="n">
-        <v>4.26</v>
+        <v>11.94</v>
       </c>
       <c r="O23" t="n">
         <v>-7.09</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>180.7</v>
+        <v>177</v>
       </c>
       <c r="I24" t="n">
         <v>180.6478530418629</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>13.58</v>
+        <v>11.25</v>
       </c>
       <c r="L24" t="n">
         <v>4.15</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45196.38541666666</v>
+        <v>45196.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>187.4</v>
+        <v>193.3</v>
       </c>
       <c r="I25" t="n">
         <v>189.7573504423462</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.88</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>7.68</v>
+        <v>11.07</v>
       </c>
       <c r="M25" t="n">
         <v>1.56</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.65</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45237.38541666666</v>
+        <v>45237.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>255.2</v>
+        <v>254.5</v>
       </c>
       <c r="I26" t="n">
         <v>255.0194821592498</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>32.02</v>
+        <v>31.66</v>
       </c>
       <c r="L26" t="n">
         <v>5.64</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.89</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>280.1</v>
+        <v>293.4</v>
       </c>
       <c r="I27" t="n">
         <v>284.7692377553162</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-10.06</v>
+        <v>-15.28</v>
       </c>
       <c r="L27" t="n">
-        <v>11.2</v>
+        <v>17.45</v>
       </c>
       <c r="M27" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="N27" t="n">
-        <v>5.27</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>-2.97</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>10.23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45306.55208333334</v>
+        <v>45307.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>384.5</v>
+        <v>338.6</v>
       </c>
       <c r="I28" t="n">
         <v>357.1526520738455</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K28" t="n">
-        <v>31.05</v>
+        <v>15.41</v>
       </c>
       <c r="L28" t="n">
         <v>3.41</v>
       </c>
       <c r="M28" t="n">
-        <v>3.64</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>3.64</v>
+        <v>12.9</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>14.55</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45321.55208333334</v>
+        <v>45322.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>310.4</v>
+        <v>324</v>
       </c>
       <c r="I29" t="n">
         <v>322.6386078629334</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>8.33</v>
+        <v>4.31</v>
       </c>
       <c r="L29" t="n">
         <v>6.47</v>
@@ -2094,7 +2441,7 @@
         <v>1.33</v>
       </c>
       <c r="N29" t="n">
-        <v>5.26</v>
+        <v>5.67</v>
       </c>
       <c r="O29" t="n">
         <v>-12.9</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>13.2</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45343.55208333334</v>
+        <v>45344.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>309</v>
+        <v>306.9</v>
       </c>
       <c r="I30" t="n">
         <v>308.5402710613711</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.63</v>
+        <v>-5.28</v>
       </c>
       <c r="L30" t="n">
-        <v>5.56</v>
+        <v>6.3</v>
       </c>
       <c r="M30" t="n">
         <v>1.47</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.09</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45377.38541666666</v>
+        <v>45377.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>268.1</v>
+        <v>275</v>
       </c>
       <c r="I31" t="n">
         <v>268.9434731005837</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>12.64</v>
+        <v>10.39</v>
       </c>
       <c r="L31" t="n">
         <v>2.41</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>10.9</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>288.2</v>
+        <v>282.3</v>
       </c>
       <c r="I32" t="n">
         <v>285.0075838689918</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="L32" t="n">
         <v>3.49</v>
       </c>
       <c r="M32" t="n">
-        <v>1.22</v>
+        <v>3.37</v>
       </c>
       <c r="N32" t="n">
         <v>4.44</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.35</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45426.55208333334</v>
+        <v>45427.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>262</v>
+        <v>266.5</v>
       </c>
       <c r="I33" t="n">
         <v>265.3603747727493</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K33" t="n">
-        <v>7.19</v>
+        <v>5.6</v>
       </c>
       <c r="L33" t="n">
         <v>9.81</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>10.57</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45439.55208333334</v>
+        <v>45440.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>258.5</v>
+        <v>254.3</v>
       </c>
       <c r="I34" t="n">
         <v>257.6378248088087</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K34" t="n">
-        <v>-3</v>
+        <v>-4.58</v>
       </c>
       <c r="L34" t="n">
-        <v>3.83</v>
+        <v>4.99</v>
       </c>
       <c r="M34" t="n">
         <v>0.11</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>252.4</v>
+        <v>257.6</v>
       </c>
       <c r="I35" t="n">
         <v>256.5076511109088</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>0.75</v>
+        <v>-1.3</v>
       </c>
       <c r="L35" t="n">
         <v>4.09</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>12.14</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>257.9</v>
+        <v>235.8</v>
       </c>
       <c r="I36" t="n">
         <v>246.6501528277862</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>0.12</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>2.76</v>
+        <v>10.21</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5</v>
+        <v>8.49</v>
       </c>
       <c r="N36" t="n">
-        <v>1.79</v>
+        <v>8.49</v>
       </c>
       <c r="O36" t="n">
         <v>2.46</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.34</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="I37" t="n">
         <v>224.0787781855178</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>10.94</v>
+        <v>4.58</v>
       </c>
       <c r="L37" t="n">
         <v>3.86</v>
@@ -2550,7 +2993,7 @@
         <v>1.47</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>5.95</v>
       </c>
       <c r="O37" t="n">
         <v>-8.49</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.68</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45510.38541666666</v>
+        <v>45510.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>208.9</v>
+        <v>205.7</v>
       </c>
       <c r="I38" t="n">
         <v>206.2177877950654</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.16</v>
+        <v>-8.58</v>
       </c>
       <c r="L38" t="n">
         <v>10</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.1</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45520.55208333334</v>
+        <v>45523.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>214.9</v>
+        <v>236.6</v>
       </c>
       <c r="I39" t="n">
         <v>225.5307480325182</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.47</v>
+        <v>-15.02</v>
       </c>
       <c r="L39" t="n">
-        <v>7.34</v>
+        <v>15.7</v>
       </c>
       <c r="M39" t="n">
-        <v>1.23</v>
+        <v>2.14</v>
       </c>
       <c r="N39" t="n">
-        <v>4.72</v>
+        <v>9.68</v>
       </c>
       <c r="O39" t="n">
         <v>-3.15</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.06</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>240.1</v>
+        <v>238.9</v>
       </c>
       <c r="I40" t="n">
         <v>240.0743156652289</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K40" t="n">
-        <v>1.48</v>
+        <v>0.97</v>
       </c>
       <c r="L40" t="n">
         <v>8.07</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>7.15</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45551.38541666666</v>
+        <v>45551.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>249</v>
+        <v>257.5</v>
       </c>
       <c r="I41" t="n">
         <v>255.988022124763</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.23</v>
+        <v>-7.79</v>
       </c>
       <c r="L41" t="n">
-        <v>5.78</v>
+        <v>10.42</v>
       </c>
       <c r="M41" t="n">
         <v>1.1</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.01</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>287.5</v>
+        <v>281.6</v>
       </c>
       <c r="I42" t="n">
         <v>283.8189124558445</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>11.65</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>5.05</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.73</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45622.38541666666</v>
+        <v>45622.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>280.6</v>
+        <v>293.6</v>
       </c>
       <c r="I43" t="n">
         <v>287.0616665900591</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>0.36</v>
+        <v>-4.26</v>
       </c>
       <c r="L43" t="n">
         <v>10.94</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.87</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>321.1</v>
+        <v>315.9</v>
       </c>
       <c r="I44" t="n">
         <v>320.55408660838</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>9.369999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L44" t="n">
         <v>4.8</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45689.38541666666</v>
+        <v>45689.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>231.6</v>
+        <v>248.4</v>
       </c>
       <c r="I45" t="n">
         <v>245.7328021618572</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>45.83333333333334</v>
+        <v>46</v>
       </c>
       <c r="K45" t="n">
-        <v>26.69</v>
+        <v>21.37</v>
       </c>
       <c r="L45" t="n">
         <v>1.77</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>13.89</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>234.9</v>
+        <v>221.6</v>
       </c>
       <c r="I46" t="n">
         <v>223.7583441499816</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.43</v>
+        <v>-10.79</v>
       </c>
       <c r="L46" t="n">
-        <v>7.53</v>
+        <v>10.87</v>
       </c>
       <c r="M46" t="n">
         <v>2.42</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.11</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>209.4</v>
+        <v>219.7</v>
       </c>
       <c r="I47" t="n">
         <v>212.9421983586772</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K47" t="n">
-        <v>5.51</v>
+        <v>0.86</v>
       </c>
       <c r="L47" t="n">
         <v>10.15</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>10.41</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>228</v>
+        <v>209.2</v>
       </c>
       <c r="I48" t="n">
         <v>224.1556811944534</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>3.78</v>
+        <v>-4.78</v>
       </c>
       <c r="L48" t="n">
-        <v>4.6</v>
+        <v>6.37</v>
       </c>
       <c r="M48" t="n">
-        <v>1.66</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N48" t="n">
         <v>7.65</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>13.35</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>234.9</v>
+        <v>249.6</v>
       </c>
       <c r="I49" t="n">
         <v>237.1228084092434</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-12.28</v>
+        <v>-19.31</v>
       </c>
       <c r="L49" t="n">
-        <v>14.05</v>
+        <v>20.65</v>
       </c>
       <c r="M49" t="n">
         <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>3.57</v>
+        <v>5.15</v>
       </c>
       <c r="O49" t="n">
         <v>-5.53</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.6</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>305.6</v>
+        <v>300.8</v>
       </c>
       <c r="I50" t="n">
         <v>304.2105524514026</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>22.44</v>
+        <v>20.51</v>
       </c>
       <c r="L50" t="n">
         <v>9.74</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.7</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>264.1</v>
+        <v>267.7</v>
       </c>
       <c r="I51" t="n">
         <v>265.814204841193</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>63</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>12.2</v>
+        <v>11</v>
       </c>
       <c r="L51" t="n">
         <v>2.16</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.51</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45890.38541666666</v>
+        <v>45890.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>257.8</v>
+        <v>254.6</v>
       </c>
       <c r="I52" t="n">
         <v>256.2948882838009</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.7</v>
+        <v>-4.89</v>
       </c>
       <c r="L52" t="n">
-        <v>5.19</v>
+        <v>5.49</v>
       </c>
       <c r="M52" t="n">
         <v>0.11</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.93</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>220.5</v>
+        <v>224.9</v>
       </c>
       <c r="I53" t="n">
         <v>223.2507030178238</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>43</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>13.39</v>
+        <v>11.67</v>
       </c>
       <c r="L53" t="n">
         <v>1.65</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.94</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45985.55208333334</v>
+        <v>45986.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>268.2</v>
+        <v>267.3</v>
       </c>
       <c r="I54" t="n">
         <v>268.1864566426252</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>19.25</v>
+        <v>18.85</v>
       </c>
       <c r="L54" t="n">
         <v>3.38</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.94</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>244.2</v>
+        <v>250.4</v>
       </c>
       <c r="I55" t="n">
         <v>247.9790138134083</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K55" t="n">
-        <v>8.640000000000001</v>
+        <v>6.32</v>
       </c>
       <c r="L55" t="n">
         <v>5.69</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46045.38541666666</v>
+        <v>46045.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>255.1</v>
+        <v>250.9</v>
       </c>
       <c r="I56" t="n">
         <v>252.3989845608102</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>1.88</v>
+        <v>0.2</v>
       </c>
       <c r="L56" t="n">
         <v>2.76</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>240</v>
+        <v>260.1</v>
       </c>
       <c r="I57" t="n">
         <v>258.9441046447734</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>4.34</v>
+        <v>-3.67</v>
       </c>
       <c r="L57" t="n">
-        <v>5.14</v>
+        <v>6.18</v>
       </c>
       <c r="M57" t="n">
-        <v>0.24</v>
+        <v>4.17</v>
       </c>
       <c r="N57" t="n">
-        <v>3.54</v>
+        <v>7.92</v>
       </c>
       <c r="O57" t="n">
         <v>-2.41</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>13.13</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46066.55208333334</v>
+        <v>46069.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>268.9</v>
+        <v>255.6</v>
       </c>
       <c r="I58" t="n">
         <v>258.401253382694</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>3.38</v>
+        <v>-1.73</v>
       </c>
       <c r="L58" t="n">
-        <v>3.88</v>
+        <v>6.15</v>
       </c>
       <c r="M58" t="n">
-        <v>1.63</v>
+        <v>5.91</v>
       </c>
       <c r="N58" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="O58" t="n">
         <v>7.92</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>217.2</v>
+        <v>234.12</v>
       </c>
       <c r="I59" t="n">
         <v>232.3039809410674</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>15.02</v>
+        <v>8.4</v>
       </c>
       <c r="L59" t="n">
         <v>3.87</v>
@@ -3804,7 +4511,7 @@
         <v>1.45</v>
       </c>
       <c r="N59" t="n">
-        <v>2.82</v>
+        <v>8.75</v>
       </c>
       <c r="O59" t="n">
         <v>-4.8</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>12.56</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>318</v>
+        <v>304.15</v>
       </c>
       <c r="I60" t="n">
         <v>304.7303502898185</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K60" t="n">
-        <v>35.83</v>
+        <v>29.91</v>
       </c>
       <c r="L60" t="n">
         <v>7.24</v>
@@ -3861,7 +4580,7 @@
         <v>3.12</v>
       </c>
       <c r="N60" t="n">
-        <v>4.16</v>
+        <v>5.64</v>
       </c>
       <c r="O60" t="n">
         <v>8.75</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.57</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46160.55208333334</v>
+        <v>46161.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>304.6</v>
+        <v>322.6</v>
       </c>
       <c r="I61" t="n">
         <v>320.4085066121691</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.15</v>
+        <v>-6.07</v>
       </c>
       <c r="L61" t="n">
-        <v>3.88</v>
+        <v>6.53</v>
       </c>
       <c r="M61" t="n">
         <v>0.77</v>
       </c>
       <c r="N61" t="n">
-        <v>2.3</v>
+        <v>8.17</v>
       </c>
       <c r="O61" t="n">
         <v>-5.64</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.62</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>330.25</v>
+        <v>323.95</v>
       </c>
       <c r="I62" t="n">
         <v>324.8702742594295</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>2.37</v>
+        <v>0.42</v>
       </c>
       <c r="L62" t="n">
         <v>5.8</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>9.02</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>339</v>
+        <v>353.65</v>
       </c>
       <c r="I63" t="n">
         <v>349.4469016989913</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.65</v>
+        <v>-9.17</v>
       </c>
       <c r="L63" t="n">
-        <v>5.05</v>
+        <v>9.94</v>
       </c>
       <c r="M63" t="n">
         <v>1.5</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>9.09</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>335.5</v>
+        <v>328.9</v>
       </c>
       <c r="I64" t="n">
         <v>332.4090050424145</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.13</v>
+        <v>-7</v>
       </c>
       <c r="L64" t="n">
-        <v>5.36</v>
+        <v>7.51</v>
       </c>
       <c r="M64" t="n">
-        <v>0.42</v>
+        <v>0.89</v>
       </c>
       <c r="N64" t="n">
         <v>3.17</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>7.81</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>347.05</v>
+        <v>354.35</v>
       </c>
       <c r="I65" t="n">
         <v>350.6151254122659</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>-5.52</v>
+        <v>-7.74</v>
       </c>
       <c r="L65" t="n">
-        <v>5.76</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M65" t="n">
         <v>0.27</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>8.06</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46219.55208333334</v>
+        <v>46220.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>334.75</v>
+        <v>327.1</v>
       </c>
       <c r="I66" t="n">
         <v>330.6897874699818</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.53</v>
+        <v>-7.69</v>
       </c>
       <c r="L66" t="n">
-        <v>7.56</v>
+        <v>8.83</v>
       </c>
       <c r="M66" t="n">
         <v>1.2</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.24</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46259.38541666666</v>
+        <v>46259.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>294.1</v>
+        <v>300.9</v>
       </c>
       <c r="I67" t="n">
         <v>300.5612799849048</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K67" t="n">
-        <v>10.09</v>
+        <v>8.01</v>
       </c>
       <c r="L67" t="n">
         <v>3.15</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.79</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>286.35</v>
+        <v>283.25</v>
       </c>
       <c r="I68" t="n">
         <v>284.739340932926</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.84</v>
+        <v>-5.87</v>
       </c>
       <c r="L68" t="n">
         <v>7.53</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.28</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46268.55208333334</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>286</v>
+        <v>299.4</v>
       </c>
       <c r="I69" t="n">
         <v>295.5489788359463</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.97</v>
+        <v>-5.7</v>
       </c>
       <c r="L69" t="n">
-        <v>1.77</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M69" t="n">
-        <v>0.48</v>
+        <v>3.18</v>
       </c>
       <c r="N69" t="n">
-        <v>2.51</v>
+        <v>4.56</v>
       </c>
       <c r="O69" t="n">
         <v>-1.68</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.74</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>288</v>
+        <v>279.6</v>
       </c>
       <c r="I70" t="n">
         <v>285.2940538458761</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.81</v>
+        <v>-6.61</v>
       </c>
       <c r="L70" t="n">
-        <v>4.31</v>
+        <v>7.13</v>
       </c>
       <c r="M70" t="n">
         <v>1.22</v>
       </c>
       <c r="N70" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="O70" t="n">
         <v>4.56</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>6.88</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>283.75</v>
+        <v>294</v>
       </c>
       <c r="I71" t="n">
         <v>288.7797508121504</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.48</v>
+        <v>-5.15</v>
       </c>
       <c r="L71" t="n">
-        <v>2.43</v>
+        <v>5.4</v>
       </c>
       <c r="M71" t="n">
-        <v>0.93</v>
+        <v>1.81</v>
       </c>
       <c r="N71" t="n">
-        <v>3.46</v>
+        <v>4.02</v>
       </c>
       <c r="O71" t="n">
         <v>-3.06</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>7.4</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>291.35</v>
+        <v>277.55</v>
       </c>
       <c r="I72" t="n">
         <v>288.3865440196565</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.9</v>
+        <v>-5.6</v>
       </c>
       <c r="L72" t="n">
-        <v>2.76</v>
+        <v>5.94</v>
       </c>
       <c r="M72" t="n">
         <v>1.02</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,12 @@
       <c r="Q73" t="n">
         <v>6</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +7588,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6717,7 +7598,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6727,7 +7608,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -6737,7 +7618,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6747,7 +7628,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.6</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="10">
@@ -6757,7 +7638,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -6797,7 +7678,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.28</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="15">
@@ -6807,7 +7688,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.51</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="16">
@@ -6817,7 +7698,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.02</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="17">
@@ -6827,7 +7708,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35.83</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="18">
@@ -6837,7 +7718,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="19">
@@ -6847,7 +7728,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.21</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="20">
@@ -6857,7 +7738,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.6</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="21">
@@ -6867,7 +7748,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.05</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="22">
@@ -6877,7 +7758,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -6887,7 +7768,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +7778,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="25">
@@ -6907,7 +7788,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.199999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -6917,7 +7798,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.57</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="27">
@@ -6927,7 +7808,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.79</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="28">
@@ -6937,7 +7818,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
